--- a/data/trans_dic/P05A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P05A_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,03; 37,15</t>
+          <t>29,64; 37,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,27; 43,04</t>
+          <t>35,3; 42,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,17; 41,61</t>
+          <t>34,55; 41,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,23; 9,84</t>
+          <t>5,22; 9,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,71; 40,95</t>
+          <t>33,84; 40,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,29; 42,14</t>
+          <t>34,24; 41,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,19; 42,31</t>
+          <t>34,83; 42,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 7,92</t>
+          <t>5,16; 8,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,1; 38,08</t>
+          <t>33,07; 38,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,78; 41,12</t>
+          <t>35,81; 41,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35,6; 41,04</t>
+          <t>35,53; 40,9</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 8,0</t>
+          <t>5,46; 8,13</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,67; 33,0</t>
+          <t>26,88; 32,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,71; 34,62</t>
+          <t>28,66; 34,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,74; 33,49</t>
+          <t>27,46; 33,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 13,66</t>
+          <t>9,6; 14,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,3; 39,9</t>
+          <t>33,13; 39,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,01; 35,31</t>
+          <t>29,13; 35,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,45; 33,33</t>
+          <t>27,46; 33,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,34; 16,44</t>
+          <t>12,32; 16,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,96; 35,36</t>
+          <t>30,86; 35,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,74; 34,15</t>
+          <t>29,73; 33,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,35; 32,61</t>
+          <t>28,34; 32,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,78; 13,91</t>
+          <t>11,44; 14,42</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,69; 31,83</t>
+          <t>24,88; 31,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,64; 42,32</t>
+          <t>35,03; 42,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,52; 42,79</t>
+          <t>35,38; 42,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,28; 22,55</t>
+          <t>16,01; 22,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,35; 31,1</t>
+          <t>24,69; 31,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,51; 43,97</t>
+          <t>36,44; 43,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,11; 43,25</t>
+          <t>35,78; 43,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,4; 67,44</t>
+          <t>17,01; 22,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,45; 30,35</t>
+          <t>25,51; 30,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,71; 41,89</t>
+          <t>36,7; 41,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37,02; 41,9</t>
+          <t>36,83; 42,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,83; 52,81</t>
+          <t>17,11; 21,26</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,49; 30,35</t>
+          <t>24,59; 30,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,5; 53,11</t>
+          <t>46,71; 53,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,82; 41,35</t>
+          <t>34,87; 41,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,52; 36,29</t>
+          <t>30,45; 36,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,08; 37,87</t>
+          <t>31,92; 37,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,33; 51,51</t>
+          <t>45,3; 51,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,63; 42,65</t>
+          <t>36,28; 42,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,26; 35,63</t>
+          <t>33,69; 38,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,5; 33,66</t>
+          <t>29,55; 33,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46,67; 51,36</t>
+          <t>46,9; 51,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,51; 40,86</t>
+          <t>36,42; 40,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,71; 34,72</t>
+          <t>33,0; 37,03</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,05; 31,38</t>
+          <t>28,09; 31,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,02; 41,34</t>
+          <t>37,95; 41,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,35; 37,62</t>
+          <t>34,32; 37,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,49; 19,13</t>
+          <t>17,07; 19,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,78; 36,09</t>
+          <t>32,88; 36,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,27; 41,63</t>
+          <t>38,26; 41,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,87; 38,24</t>
+          <t>34,91; 38,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,74; 38,91</t>
+          <t>19,33; 21,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,91; 33,3</t>
+          <t>30,77; 33,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38,58; 41,1</t>
+          <t>38,48; 40,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35,17; 37,43</t>
+          <t>35,15; 37,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,58; 28,84</t>
+          <t>18,6; 20,44</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46075</t>
+          <t>48946</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43574</t>
+          <t>47321</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89648</t>
+          <t>96267</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>208433; 257791</t>
+          <t>205690; 258355</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>247320; 301788</t>
+          <t>247538; 298491</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>230611; 280799</t>
+          <t>233119; 281701</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33262; 62514</t>
+          <t>36026; 65902</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>232029; 281848</t>
+          <t>232954; 281499</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>238417; 293005</t>
+          <t>238098; 289836</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>236777; 284652</t>
+          <t>234353; 284016</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32633; 57480</t>
+          <t>37896; 60734</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>457580; 526417</t>
+          <t>457205; 526186</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>499736; 574303</t>
+          <t>500110; 572647</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>479815; 553092</t>
+          <t>478832; 551190</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>72139; 108871</t>
+          <t>77827; 115906</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116441</t>
+          <t>122556</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>136587</t>
+          <t>151956</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>253028</t>
+          <t>274512</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>256551; 317405</t>
+          <t>258519; 315695</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>291326; 351344</t>
+          <t>290803; 352815</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>283633; 342413</t>
+          <t>280734; 345086</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55075; 162941</t>
+          <t>100678; 147978</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>322501; 386425</t>
+          <t>320867; 381907</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>298851; 363736</t>
+          <t>300073; 364520</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>286317; 347605</t>
+          <t>286428; 344978</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>118218; 157531</t>
+          <t>131894; 173697</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>597673; 682574</t>
+          <t>595749; 680231</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>608129; 698350</t>
+          <t>607979; 694431</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>585546; 673551</t>
+          <t>585332; 675367</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>167346; 299142</t>
+          <t>242492; 305634</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129838</t>
+          <t>151732</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>340663</t>
+          <t>157028</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>470501</t>
+          <t>308760</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>167514; 215947</t>
+          <t>168835; 216480</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>262441; 320616</t>
+          <t>265430; 321399</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>269775; 325019</t>
+          <t>268704; 323200</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>107683; 158880</t>
+          <t>128349; 180121</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>166516; 212663</t>
+          <t>168865; 212721</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>283354; 341227</t>
+          <t>282849; 340028</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>282998; 338939</t>
+          <t>280418; 338301</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>162414; 629477</t>
+          <t>138166; 180410</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>346731; 413487</t>
+          <t>347497; 414634</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>563103; 642492</t>
+          <t>562939; 642838</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>571370; 646622</t>
+          <t>568319; 649271</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>292053; 864883</t>
+          <t>276148; 343175</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>302245</t>
+          <t>331759</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>354262</t>
+          <t>405002</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>656508</t>
+          <t>736761</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>230773; 285929</t>
+          <t>231714; 288837</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>440721; 503305</t>
+          <t>442730; 506717</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>326023; 387205</t>
+          <t>326523; 384030</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>273562; 336285</t>
+          <t>301155; 361862</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>333190; 393295</t>
+          <t>331547; 393666</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>476396; 541374</t>
+          <t>476064; 542329</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>381963; 444748</t>
+          <t>378310; 445140</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>287367; 389825</t>
+          <t>376733; 434461</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>584305; 666687</t>
+          <t>585286; 663785</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>932867; 1026486</t>
+          <t>937449; 1025773</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>722597; 808714</t>
+          <t>720679; 809856</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>580157; 701612</t>
+          <t>695491; 780378</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>594599</t>
+          <t>654993</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>875086</t>
+          <t>761307</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1469685</t>
+          <t>1416300</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>919208; 1028197</t>
+          <t>920308; 1021510</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1300708; 1414412</t>
+          <t>1298317; 1417843</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1165437; 1276521</t>
+          <t>1164617; 1275558</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>466842; 661663</t>
+          <t>602590; 704913</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1107855; 1219558</t>
+          <t>1111094; 1220849</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1359477; 1478927</t>
+          <t>1359339; 1479418</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1235034; 1354433</t>
+          <t>1236745; 1356620</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>695495; 1443886</t>
+          <t>722211; 810247</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2057115; 2216172</t>
+          <t>2048095; 2207510</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2690560; 2866196</t>
+          <t>2683574; 2858180</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2438907; 2595963</t>
+          <t>2437893; 2595935</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1260212; 2067857</t>
+          <t>1351245; 1485075</t>
         </is>
       </c>
     </row>
